--- a/output/pdf_financials_xlsx/METX.xlsx
+++ b/output/pdf_financials_xlsx/METX.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/METX.xlsx
+++ b/output/pdf_financials_xlsx/METX.xlsx
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.00125</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.242233</v>
       </c>
     </row>
     <row r="10">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.984833</v>
+        <v>0.984833</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-1.373234</v>
+        <v>1.373234</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-1.28829</v>
+        <v>1.28829</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.984833</v>
+        <v>-0.984833</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1.373234</v>
+        <v>-1.373234</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.28829</v>
+        <v>-1.28829</v>
       </c>
     </row>
     <row r="12">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -856,20 +856,14 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>15.625942</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>24.361097</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>27.813056</v>
       </c>
     </row>
     <row r="27">
@@ -1298,10 +1292,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.000196</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.000157</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -2647,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3383,12 +3377,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>“Salim Dhanji”            Director                         “John Priatel”          Director</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>September 1, 2023 23,561,161 4,523,869 31,917 3,208,468</t>
+          <t>For the years ended August 31, 2025 and August</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -3398,10 +3392,10 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.523388</v>
+        <v>0.002024</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-7.240866</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="25">
@@ -3417,7 +3411,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unit offering completed 1,555,000 1,555,000 - -</t>
+          <t>September 1, 2023 23,561,161 4,523,869 31,917 3,208,468</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -3427,12 +3421,10 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.523388</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-7.240866</v>
       </c>
     </row>
     <row r="26">
@@ -3448,7 +3440,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Partial settlement of commitment 73,333 33,000 (33,000) -</t>
+          <t>Unit offering completed 1,555,000 1,555,000 - -</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3457,10 +3449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>1.555</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3481,7 +3471,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 690,891</t>
+          <t>Partial settlement of commitment 73,333 33,000 (33,000) -</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3490,8 +3480,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0.690891</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3512,7 +3504,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Commitment to issue shares - - 8,583 -</t>
+          <t>Share-based compensation - - - 690,891</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3522,7 +3514,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.008583</v>
+        <v>0.690891</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3543,7 +3535,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Settlement of commitment to issue shares in cash - - (7,500) -</t>
+          <t>Commitment to issue shares - - 8,583 -</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3553,7 +3545,7 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.008583</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3574,7 +3566,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - -</t>
+          <t>Settlement of commitment to issue shares in cash - - (7,500) -</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3584,10 +3576,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-1.294635</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-1.294635</v>
+        <v>-0.0075</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3603,7 +3597,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>August 31, 2024 25,189,494 6,111,869 - 3,899,359</t>
+          <t>Loss and comprehensive loss for the year - - - -</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3613,10 +3607,10 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1.475727</v>
+        <v>-1.294635</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-8.535501</v>
+        <v>-1.294635</v>
       </c>
     </row>
     <row r="32">
@@ -3632,7 +3626,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>September 1, 2024 25,189,494 6,111,869 - 3,899,359</t>
+          <t>August 31, 2024 25,189,494 6,111,869 - 3,899,359</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3661,7 +3655,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exercise of warrants 4,400,000 1,050,000 - -</t>
+          <t>September 1, 2024 25,189,494 6,111,869 - 3,899,359</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3671,12 +3665,10 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.475727</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-8.535501</v>
       </c>
     </row>
     <row r="34">
@@ -3692,7 +3684,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fair value reversal on exercise of warrants - 1,428,022 - (1,428,022)</t>
+          <t>Exercise of warrants 4,400,000 1,050,000 - -</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3701,10 +3693,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>1.05</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3725,7 +3715,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - 170,574</t>
+          <t>Fair value reversal on exercise of warrants - 1,428,022 - (1,428,022)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -3734,8 +3724,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0.170574</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3756,7 +3748,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>August 31, 2025 29,589,494 8,589,891 - 2,641,911</t>
+          <t>Share-based compensation - - - 170,574</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3766,10 +3758,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1.503101</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>-9.728700999999999</v>
+        <v>0.170574</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3778,23 +3772,27 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>As at August 31, 2024 and August</t>
+          <t>August 31, 2025 29,589,494 8,589,891 - 2,641,911</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>0.002023</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.503101</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>-9.728700999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3803,22 +3801,18 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Non-current assets</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Equipment 4</t>
+          <t>As at August 31, 2024 and August</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.000196</v>
+        <v>0.002023</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.000157</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3834,22 +3828,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Government loans 12</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Equipment 4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000196</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.000157</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3870,19 +3866,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
+          <t>Government loans 12</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.148473</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.062918</v>
+        <v>0.04</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3898,22 +3892,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Commitment to issue shares 6,7</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.031917</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.148473</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.062918</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3929,20 +3925,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>September 1, 2022 8,488,458 513,082 - 18,263 57,649</t>
+          <t>Commitment to issue shares 6,7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>-0.131482</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-0.720476</v>
+        <v>0.031917</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3958,22 +3956,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>“Salim Dhanji”            Director                         “John Priatel”          Director</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Conversion of convertible debentures 6,511,536 158,262 - (18,263) -</t>
+          <t>For the years ended August 31, 2024 and August</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.139999</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3989,22 +3985,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reverse acquisition transaction</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Equity of ME Therapeutics Holdings Inc. 8,304,445 3,737,000 - - -</t>
+          <t>September 1, 2022 8,488,458 513,082 - 18,263 57,649</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.131482</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-0.720476</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4020,17 +4014,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Reverse acquisition transaction</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fair value of retained warrants - - - - 2,562,600</t>
+          <t>Conversion of convertible debentures 6,511,536 158,262 - (18,263) -</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>2.5626</v>
+        <v>0.139999</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4056,12 +4050,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Common share financing 256,722 115,525 - - -</t>
+          <t>Equity of ME Therapeutics Holdings Inc. 8,304,445 3,737,000 - - -</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.115525</v>
+        <v>3.737</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4087,12 +4081,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - - 588,219</t>
+          <t>Fair value of retained warrants - - - - 2,562,600</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0.588219</v>
+        <v>2.5626</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4118,12 +4112,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Commitment to issue shares - - 31,917 - -</t>
+          <t>Common share financing 256,722 115,525 - - -</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.031917</v>
+        <v>0.115525</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4149,15 +4143,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - - -</t>
+          <t>Share-based compensation - - - - 588,219</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>-6.52039</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-6.52039</v>
+        <v>0.588219</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4178,15 +4174,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>August 31, 2023 23,561,161 4,523,869 31,917 - 3,208,468</t>
+          <t>Commitment to issue shares - - 31,917 - -</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>0.523388</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-7.240866</v>
+        <v>0.031917</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4207,15 +4205,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>September 1, 2023 23,561,161 4,523,869 31,917 - 3,208,468</t>
+          <t>Loss and comprehensive loss for the year - - - - -</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>0.523388</v>
+        <v>-6.52039</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>-7.240866</v>
+        <v>-6.52039</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4236,17 +4234,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unit offering completed 1,555,000 1,555,000 - - -</t>
+          <t>August 31, 2023 23,561,161 4,523,869 31,917 - 3,208,468</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.523388</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>-7.240866</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4267,19 +4263,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Partial settlement of commitment 73,333 33,000 (33,000) - -</t>
+          <t>September 1, 2023 23,561,161 4,523,869 31,917 - 3,208,468</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>0.523388</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-7.240866</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4300,12 +4292,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share-based compensation - - - - 690,891</t>
+          <t>Unit offering completed 1,555,000 1,555,000 - - -</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.690891</v>
+        <v>1.555</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4331,12 +4323,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Commitment to issue shares - - 8,583 - -</t>
+          <t>Partial settlement of commitment 73,333 33,000 (33,000) - -</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>0.008583</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4362,12 +4356,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Settlement of commitment to issue shares in cash - - (7,500) - -</t>
+          <t>Share-based compensation - - - - 690,891</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.690891</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4393,15 +4387,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>August 31, 2024 25,189,494 6,111,869 - - 3,899,359</t>
+          <t>Commitment to issue shares - - 8,583 - -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>1.475727</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>-8.535501</v>
+        <v>0.008583</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -4412,63 +4408,61 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Reverse acquisition transaction</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Settlement of commitment to issue shares in cash - - (7,500) - -</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>-6.52039</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-1.294635</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-1.1932</v>
+        <v>-0.0075</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Reverse acquisition transaction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>August 31, 2024 25,189,494 6,111,869 - - 3,899,359</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>1.475727</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>3.9e-05</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.083319</v>
+        <v>-8.535501</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4479,27 +4473,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Finance charges</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>-6.52039</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-1.294635</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.012717</v>
+        <v>-1.1932</v>
       </c>
     </row>
     <row r="61">
@@ -4515,22 +4509,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.588219</v>
+        <v>4.9e-05</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.690891</v>
+        <v>3.9e-05</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.170574</v>
+        <v>0.083319</v>
       </c>
     </row>
     <row r="62">
@@ -4546,20 +4540,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Commitment to issue shares - services</t>
+          <t>Finance charges</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.031917</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.008583</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.012717</v>
       </c>
     </row>
     <row r="63">
@@ -4570,23 +4566,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sales tax receivable</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
-        <v>-0.001578</v>
+        <v>0.588219</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-0.00937</v>
+        <v>0.690891</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.027419</v>
+        <v>0.170574</v>
       </c>
     </row>
     <row r="64">
@@ -4597,25 +4597,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Working capital adjustments</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Government assistance receivable</t>
+          <t>Commitment to issue shares - services</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>-0.024193</v>
+        <v>0.031917</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.008583</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4631,22 +4631,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Sales tax receivable</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>-0.015102</v>
+        <v>-0.001578</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-0.007873</v>
+        <v>-0.00937</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.005835</v>
+        <v>-0.027419</v>
       </c>
     </row>
     <row r="66">
@@ -4662,22 +4658,20 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Government assistance receivable</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>0.058289</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.060578</v>
+        <v>0.017</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.10907</v>
+        <v>-0.024193</v>
       </c>
     </row>
     <row r="67">
@@ -4693,18 +4687,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Due to related parties</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
-        <v>-0.016029</v>
+        <v>-0.015102</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.015023</v>
+        <v>-0.007873</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.01262</v>
+        <v>-0.005835</v>
       </c>
     </row>
     <row r="68">
@@ -4720,18 +4718,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Working capital adjustments total</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>-0.303195</v>
+        <v>0.058289</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.6579199999999999</v>
+        <v>-0.060578</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.862347</v>
+        <v>0.10907</v>
       </c>
     </row>
     <row r="69">
@@ -4742,27 +4744,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants</t>
+          <t>Due to related parties</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>-0.016029</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.015023</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>1.05</v>
+        <v>0.01262</v>
       </c>
     </row>
     <row r="70">
@@ -4773,27 +4771,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Working capital adjustments</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unit offering completed</t>
+          <t>Working capital adjustments total</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="5" t="n">
+        <v>-0.303195</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.6579199999999999</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.862347</v>
       </c>
     </row>
     <row r="71">
@@ -4809,7 +4803,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Settlement of share commitment for cash</t>
+          <t>Proceeds from exercise of warrants</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -4818,13 +4812,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="72">
@@ -4840,7 +4834,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Repayment of Government loans</t>
+          <t>Unit offering completed</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4850,7 +4844,7 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.04</v>
+        <v>1.555</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4871,7 +4865,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Payment of lease liabilities 4</t>
+          <t>Settlement of share commitment for cash</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -4880,13 +4874,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>-0.054457</v>
+      <c r="F73" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4902,22 +4896,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>0.115525</v>
+          <t>Repayment of Government loans</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1.5075</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>0.995543</v>
+        <v>-0.04</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4928,12 +4922,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Short-term investment</t>
+          <t>Payment of lease liabilities 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -4948,7 +4942,7 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0575</v>
+        <v>-0.054457</v>
       </c>
     </row>
     <row r="76">
@@ -4959,27 +4953,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Payment of security deposit 4</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0.115525</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>1.5075</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.010891</v>
+        <v>0.995543</v>
       </c>
     </row>
     <row r="77">
@@ -4995,7 +4989,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Short-term investment</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5010,7 +5004,7 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.216153</v>
+        <v>-0.0575</v>
       </c>
     </row>
     <row r="78">
@@ -5026,16 +5020,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Investing activities total</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>0.7574379999999999</v>
+          <t>Payment of security deposit 4</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -5043,7 +5035,7 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.284544</v>
+        <v>-0.010891</v>
       </c>
     </row>
     <row r="79">
@@ -5059,22 +5051,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>0.5697680000000001</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.84958</v>
+          <t>Purchase of equipment</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.151348</v>
+        <v>-0.216153</v>
       </c>
     </row>
     <row r="80">
@@ -5090,22 +5082,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Investing activities total</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.077377</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.647145</v>
+        <v>0.7574379999999999</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1.496725</v>
+        <v>-0.284544</v>
       </c>
     </row>
     <row r="81">
@@ -5121,22 +5115,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0.647145</v>
+        <v>0.5697680000000001</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>1.496725</v>
+        <v>0.84958</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1.345377</v>
+        <v>-0.151348</v>
       </c>
     </row>
     <row r="82">
@@ -5152,18 +5146,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>0.077377</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0</v>
+        <v>0.647145</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1e-06</v>
+        <v>1.496725</v>
       </c>
     </row>
     <row r="83">
@@ -5174,27 +5172,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Interest/accretion - convertible debentures</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
-        <v>0.007462</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.647145</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1.496725</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>1.345377</v>
       </c>
     </row>
     <row r="84">
@@ -5210,12 +5208,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Transaction expense</t>
+          <t>Interest/accretion - convertible debentures</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>5.566968</v>
+        <v>0.007462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5241,12 +5239,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Transaction expense</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>-0.02</v>
+        <v>5.566968</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5267,20 +5265,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Unit/share offering completed</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>0.115525</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>1.555</v>
+        <v>-0.02</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5301,17 +5301,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Settlement of share commitment for cash 6,7</t>
+          <t>Unit/share offering completed</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>0.115525</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.0075</v>
+        <v>1.555</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5332,7 +5330,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Repayment of Government loans 12</t>
+          <t>Settlement of share commitment for cash 6,7</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -5342,7 +5340,7 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.0075</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5358,22 +5356,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cash acquired on reverse acquisition 3</t>
+          <t>Repayment of Government loans 12</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" s="5" t="n">
-        <v>0.7574379999999999</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-0.04</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5384,28 +5382,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Consulting 7</t>
+          <t>Cash acquired on reverse acquisition 3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
-        <v>0.00125</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>0.242233</v>
+        <v>0.7574379999999999</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5421,24 +5423,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Depreciation 4</t>
+          <t>Consulting 7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.00125</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>3.9e-05</v>
+        <v>0.055</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.083319</v>
+        <v>0.242233</v>
       </c>
     </row>
     <row r="92">
@@ -5454,22 +5454,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Finance charges 4</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation 4</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>4.9e-05</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>3.9e-05</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.012717</v>
+        <v>0.083319</v>
       </c>
     </row>
     <row r="93">
@@ -5485,24 +5485,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Finance charges 4</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>0.111233</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.129894</v>
+        <v>0.012717</v>
       </c>
     </row>
     <row r="94">
@@ -5518,22 +5516,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Professional fees 7</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.33597</v>
+        <v>0.024766</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.20405</v>
+        <v>0.111233</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.23742</v>
+        <v>0.129894</v>
       </c>
     </row>
     <row r="95">
@@ -5549,20 +5547,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Research costs</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 7</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0.33597</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.312021</v>
+        <v>0.20405</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.412133</v>
+        <v>0.23742</v>
       </c>
     </row>
     <row r="96">
@@ -5578,18 +5578,18 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Share-based compensation 6,7</t>
+          <t>Research costs</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
-        <v>0.588219</v>
+        <v>0.027117</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.690891</v>
+        <v>0.312021</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.170574</v>
+        <v>0.412133</v>
       </c>
     </row>
     <row r="97">
@@ -5605,22 +5605,18 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Loss from operating expenses</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation 6,7</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" s="5" t="n">
-        <v>-0.984833</v>
+        <v>0.588219</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>-1.373234</v>
+        <v>0.690891</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>-1.28829</v>
+        <v>0.170574</v>
       </c>
     </row>
     <row r="98">
@@ -5636,22 +5632,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Loss from operating expenses</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.011411</v>
+        <v>0.984833</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.031817</v>
+        <v>1.373234</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.037802</v>
+        <v>1.28829</v>
       </c>
     </row>
     <row r="99">
@@ -5667,20 +5663,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Government assistance 12</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0.011411</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.046782</v>
+        <v>0.031817</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.057288</v>
+        <v>0.037802</v>
       </c>
     </row>
     <row r="100">
@@ -5696,22 +5694,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>-6.52039</v>
+          <t>Government assistance 12</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-1.294635</v>
+        <v>0.046782</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-1.1932</v>
+        <v>0.057288</v>
       </c>
     </row>
     <row r="101">
@@ -5722,23 +5718,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>- Basic #</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
-        <v>15.625942</v>
+        <v>-6.52039</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>24.361097</v>
+        <v>-1.294635</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>27.813056</v>
+        <v>-1.1932</v>
       </c>
     </row>
     <row r="102">
@@ -5754,10 +5754,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>- Diluted #</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>- Basic #</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>15.625942</v>
       </c>
@@ -5781,18 +5785,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Basic loss per share $</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>- Diluted #</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
-        <v>-4.2e-07</v>
+        <v>15.625942</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-5e-08</v>
+        <v>24.361097</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-4e-08</v>
+        <v>27.813056</v>
       </c>
     </row>
     <row r="104">
@@ -5808,7 +5816,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Diluted loss per share $</t>
+          <t>Basic loss per share $</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -5830,29 +5838,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Depreciation 4 39</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" s="5" t="n">
-        <v>9e-06</v>
+        <v>-4.2e-07</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>-4e-08</v>
       </c>
     </row>
     <row r="106">
@@ -5868,19 +5870,17 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>General and administrative 111,233</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Interest/accretion - convertible debentures 6</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" s="5" t="n">
-        <v>0.004766</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.007462</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Interest/accretion - convertible debentures 6</t>
+          <t>Transaction expense 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" s="5" t="n">
-        <v>0.007462</v>
+        <v>-5.566968</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -5932,83 +5932,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Research costs 312,021</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Other income 12</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
-        <v>0.007117</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>2e-06</v>
+        <v>0.02</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Transaction expense 3</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>-5.566968</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Other income 12</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/METX.xlsx
+++ b/output/pdf_financials_xlsx/METX.xlsx
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.208468</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.899359</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.641911</v>
       </c>
     </row>
     <row r="93">
@@ -3265,7 +3265,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>3.208468</v>
       </c>

--- a/output/pdf_financials_xlsx/METX.xlsx
+++ b/output/pdf_financials_xlsx/METX.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.011411</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.031817</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.037802</v>
       </c>
     </row>
     <row r="13">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.52039</v>
+        <v>-6.531801</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.294635</v>
+        <v>-1.326452</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.1932</v>
+        <v>-1.231002</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.520341</v>
+        <v>-6.531752</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.294596</v>
+        <v>-1.326413</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.109881</v>
+        <v>-1.147683</v>
       </c>
     </row>
     <row r="30">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.647145</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.496725</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.345377</v>
       </c>
     </row>
     <row r="35">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.647145</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.496725</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0575</v>
+        <v>1.402877</v>
       </c>
     </row>
     <row r="37">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.664455</v>
+        <v>0.01731</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.521908</v>
+        <v>0.025183</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.400588</v>
+        <v>0.055211</v>
       </c>
     </row>
     <row r="49">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">

--- a/output/pdf_financials_xlsx/METX.xlsx
+++ b/output/pdf_financials_xlsx/METX.xlsx
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.216153</v>
       </c>
     </row>
     <row r="112">
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.216153</v>
       </c>
     </row>
     <row r="135">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.862347</v>
+        <v>-1.0785</v>
       </c>
     </row>
   </sheetData>
@@ -5058,7 +5058,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
